--- a/reports/pdf_change_20260714.xlsx
+++ b/reports/pdf_change_20260714.xlsx
@@ -47,6 +47,10 @@
       <sz val="11"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
@@ -62,10 +66,6 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -146,36 +146,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 4/7  ·  대기: KoAct, KoAct, TIGER</t>
         </is>
       </c>
     </row>
@@ -606,383 +606,399 @@
       <c r="K5" s="4" t="n"/>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 3억(100.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 2종목  /  매도 6종목</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>321980000</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>7.08%→7.96%</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>634→714</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>-70762500</v>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>0.75%→0.55%</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>321980000</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>7.08%→7.96%</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>634→714</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>-70762500</v>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>0.75%→0.55%</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
           <t>에프앤가이드</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>73185000</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>2.67%→2.87%</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>460→495</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>오로스테크놀로지</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <v>-22</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I17" s="18" t="n">
         <v>-35249500</v>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr">
         <is>
           <t>0.38%→0.28%</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>85→63</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="19" t="n"/>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="G16" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>ISC</t>
         </is>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H18" s="18" t="n">
         <v>-7</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I18" s="18" t="n">
         <v>-89964000</v>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J18" s="19" t="inlineStr">
         <is>
           <t>1.71%→1.46%</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>48→41</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="G17" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <v>-6</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I19" s="18" t="n">
         <v>-69462000</v>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>3.21%→3.02%</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>100→94</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="19" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="G18" s="16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>원익IPS</t>
         </is>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H20" s="18" t="n">
         <v>-4</v>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I20" s="18" t="n">
         <v>-42500000</v>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>2.86%→2.74%</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>97→93</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="G19" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="20" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H21" s="18" t="n">
         <v>-3</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I21" s="18" t="n">
         <v>-59160000</v>
       </c>
-      <c r="J19" s="18" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>2.57%→2.40%</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>47→44</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 9억(1.6%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="14">
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A10:K10"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260714.xlsx
+++ b/reports/pdf_change_20260714.xlsx
@@ -608,7 +608,7 @@
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
@@ -632,7 +632,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -656,7 +656,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 3억(100.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 2종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 344억   ·   현금 3억(100.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 2종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
@@ -752,11 +752,11 @@
         <v>80</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>321980000</v>
+        <v>266900000</v>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>7.08%→7.96%</t>
+          <t>6.19%→6.97%</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
@@ -773,11 +773,11 @@
         <v>-25</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>-70762500</v>
+        <v>-59818750</v>
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>0.75%→0.55%</t>
+          <t>0.66%→0.49%</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
@@ -796,11 +796,11 @@
         <v>35</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>73185000</v>
+        <v>61880000</v>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.38%→2.56%</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -817,11 +817,11 @@
         <v>-22</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>-35249500</v>
+        <v>-34782000</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -845,11 +845,11 @@
         <v>-7</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>-89964000</v>
+        <v>-91332500</v>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>1.71%→1.46%</t>
+          <t>1.83%→1.57%</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
@@ -873,11 +873,11 @@
         <v>-6</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>-69462000</v>
+        <v>-71451000</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t>3.21%→3.02%</t>
+          <t>3.48%→3.28%</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
@@ -901,11 +901,11 @@
         <v>-4</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-42500000</v>
+        <v>-42432000</v>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>2.86%→2.74%</t>
+          <t>3.01%→2.89%</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr">
@@ -929,11 +929,11 @@
         <v>-3</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>-59160000</v>
+        <v>-58522500</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t>2.57%→2.40%</t>
+          <t>2.68%→2.51%</t>
         </is>
       </c>
       <c r="K21" s="16" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 9억(1.6%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 9억(1.6%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>

--- a/reports/pdf_change_20260714.xlsx
+++ b/reports/pdf_change_20260714.xlsx
@@ -38,17 +38,8 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,6 +58,15 @@
       <b val="1"/>
       <color rgb="000070C0"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,39 +143,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: KoAct, KoAct, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 62억(1.3%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -588,379 +588,666 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>902729920</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.98%→1.16%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>493→594</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-492676800</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.44%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>177→142</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1022613120</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.22%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>0→83</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-1168080000</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>1.96%→1.44%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>199→169</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2171091200</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.05%→1.49%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>66→97</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-912144000</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>1.33%→1.15%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>202→172</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>452352000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.58%→0.68%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>70→82</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>에스앤에스텍</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-935456000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.74%→0.55%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>74→54</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>884467200</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>3.11%→3.41%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>199→211</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>비츠로셀</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-430776000</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.47%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>90→75</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>416937600</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>3.77%→4.14%</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>133→136</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-390947200</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>0.56%→0.41%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>81→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-423633600</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.46%</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>78→65</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-883872000</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>1.04%→0.88%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>61→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-410092800</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>0.85%→0.76%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>57→51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 12억(0.3%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>443206720</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.15%→1.34%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>983→1,066</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-855736000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>2.96%→2.68%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>701→652</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>1264334400</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>7.59%→7.82%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>682→709</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-409634400</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>1.79%→1.59%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>366→345</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>1124208000</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>8.20%→8.48%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>186→192</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-856032000</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>3.27%→3.08%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>195→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 344억   ·   현금 3억(100.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 2종목  /  매도 6종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>266900000</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>6.19%→6.97%</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>634→714</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-59818750</v>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>0.66%→0.49%</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>61880000</v>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>2.38%→2.56%</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>460→495</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>-34782000</v>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>0.39%→0.29%</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>85→63</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>-91332500</v>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>1.83%→1.57%</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>48→41</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="n"/>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>-71451000</v>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>3.48%→3.28%</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>100→94</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n"/>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>-42432000</v>
-      </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>3.01%→2.89%</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>97→93</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="n"/>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>-58522500</v>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>2.68%→2.51%</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>47→44</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 9억(1.6%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -969,7 +1256,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 26억(1.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -983,22 +1270,363 @@
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 344억   ·   현금 3억(100.0%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 2종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>266900000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>6.19%→6.97%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>634→714</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-59818750</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>0.66%→0.49%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>61880000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2.38%→2.56%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>460→495</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-34782000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>0.39%→0.29%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-91332500</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>1.83%→1.57%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>48→41</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-71451000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>3.48%→3.28%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>100→94</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>-42432000</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>3.01%→2.89%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>97→93</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-58522500</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>2.68%→2.51%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>47→44</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 9억(1.6%)      당일 2026-07-14  vs  전영업일 2026-07-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
